--- a/docs/downloads/经营分_河南省区__河南南片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_河南省区__河南南片区_2026-10-18.xlsx
@@ -1479,17 +1479,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6750219821515835396</t>
+          <t>6912446841397282823</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>喆啡酒店（信阳市政府火车站店）</t>
+          <t>维也纳国际酒店（5.0版信阳息县龙湖公园名扬店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>喆啡酒店(信阳市政府火车站店)</t>
+          <t>维也纳国际酒店(息县名扬店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1498,14 +1498,14 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I11" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1515,19 +1515,19 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
       </c>
       <c r="Q11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
         <v>30</v>
@@ -1567,17 +1567,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>6912446841397282823</t>
+          <t>6677343895984146436</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0版信阳息县龙湖公园名扬店）</t>
+          <t>维也纳国际酒店（信阳市政府火车站店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(息县名扬店)</t>
+          <t>维也纳国际酒店(河南信阳市政府火车站店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1589,11 +1589,11 @@
         <v>95</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1603,13 +1603,13 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
@@ -1650,22 +1650,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>信阳市</t>
+          <t>驻马店市</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6677343895984146436</t>
+          <t>6812468701317597197</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（信阳市政府火车站店）</t>
+          <t>维也纳智好酒店（驻马店新蔡神华店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(河南信阳市政府火车站店)</t>
+          <t>维也纳智好酒店(河南驻马店新蔡神华店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1677,7 +1677,7 @@
         <v>95</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1738,34 +1738,34 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>驻马店市</t>
+          <t>周口市</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6812468701317597197</t>
+          <t>6767325109129725964</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>维也纳智好酒店（驻马店新蔡神华店）</t>
+          <t>锦江之星品尚（周口淮阳太昊陵景区酒店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(河南驻马店新蔡神华店)</t>
+          <t>锦江之星品尚(周口淮阳太昊陵景区酒店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>95</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1785,13 +1785,13 @@
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>周口市</t>
+          <t>信阳市</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6767325109129725964</t>
+          <t>6601144350019684360</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>锦江之星品尚（周口淮阳太昊陵景区酒店）</t>
+          <t>7天优品（信阳息县政府路店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>锦江之星品尚(周口淮阳太昊陵景区酒店)</t>
+          <t>7天优品酒店(息县政府路店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
@@ -1879,7 +1879,7 @@
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1919,29 +1919,29 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6601144350019684360</t>
+          <t>6750219821515835396</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7天优品（信阳息县政府路店）</t>
+          <t>喆啡酒店（信阳市政府火车站店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7天优品酒店(息县政府路店)</t>
+          <t>喆啡酒店(信阳市政府火车站店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>97</v>
       </c>
       <c r="I16" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>102</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2882,38 +2882,38 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>信阳市</t>
+          <t>周口市</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7418443649803978764</t>
+          <t>7511595673469323315</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（经典版信阳东站金慧昌培训中心店）</t>
+          <t>维也纳酒店（5.0深化版周口淮阳太昊陵景区店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(信阳平桥高铁站中山古镇店)</t>
+          <t>维也纳酒店(周口淮阳太昊陵景区店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>105</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2923,7 +2923,7 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
@@ -2935,7 +2935,7 @@
         <v>30</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R27" t="n">
         <v>30</v>
@@ -2970,22 +2970,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>周口市</t>
+          <t>信阳市</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7511595673469323315</t>
+          <t>6913290461398435851</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0深化版周口淮阳太昊陵景区店）</t>
+          <t>维也纳酒店（信阳新县叶林店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>维也纳酒店(周口淮阳太昊陵景区店)</t>
+          <t>维也纳酒店(信阳新县店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -3011,7 +3011,7 @@
         <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N28" t="n">
         <v>30</v>
@@ -3023,7 +3023,7 @@
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3058,22 +3058,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>信阳市</t>
+          <t>周口市</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>6913290461398435851</t>
+          <t>7220376670123853882</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>维也纳酒店（信阳新县叶林店）</t>
+          <t>锦江之星酒店（周口郸城一高新华路店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>维也纳酒店(信阳新县店)</t>
+          <t>锦江之星(郸城县新华路酒店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3085,11 +3085,11 @@
         <v>105</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3099,19 +3099,19 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>周口市</t>
+          <t>信阳市</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7220376670123853882</t>
+          <t>7045473349568301071</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>锦江之星酒店（周口郸城一高新华路店）</t>
+          <t>7天酒店（信阳火车站民权路小南门店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>锦江之星(郸城县新华路酒店)</t>
+          <t>7天酒店(信阳火车站民权路小南门店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3170,36 +3170,36 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,提质量</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
         <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N30" t="n">
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3234,42 +3234,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>信阳市</t>
+          <t>周口市</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7045473349568301071</t>
+          <t>7311990964497680396</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7天酒店（信阳火车站民权路小南门店）</t>
+          <t>7天酒店（周口五一广场市中心医院店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>7天酒店(信阳火车站民权路小南门店)</t>
+          <t>7天酒店(周口五一广场市中心医院店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>搭门店,提质量</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L31" t="n">
         <v>10</v>
@@ -3281,13 +3281,13 @@
         <v>30</v>
       </c>
       <c r="O31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P31" t="n">
         <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
@@ -3410,38 +3410,38 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>周口市</t>
+          <t>信阳市</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>7483723167639275574</t>
+          <t>7418443649803978764</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>维也纳酒店(周口太康县政府店)</t>
+          <t>维也纳国际酒店（经典版信阳东站金慧昌培训中心店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>维也纳酒店(周口太康县政府店)</t>
+          <t>维也纳国际酒店(信阳平桥高铁站中山古镇店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>110</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>提质量</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -3457,13 +3457,13 @@
         <v>30</v>
       </c>
       <c r="O33" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P33" t="n">
         <v>30</v>
       </c>
       <c r="Q33" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R33" t="n">
         <v>30</v>
@@ -3498,22 +3498,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>信阳市</t>
+          <t>周口市</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>7577588975490041892</t>
+          <t>7483723167639275574</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0信阳西亚城店）</t>
+          <t>维也纳酒店(周口太康县政府店)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>维也纳酒店(信阳西亚城店)</t>
+          <t>维也纳酒店(周口太康县政府店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -3545,13 +3545,13 @@
         <v>30</v>
       </c>
       <c r="O34" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P34" t="n">
         <v>30</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R34" t="n">
         <v>30</v>
@@ -3591,17 +3591,17 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>7192882040184768570</t>
+          <t>7577588975490041892</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>7天优品Premium（信阳固始县联通大厦店）</t>
+          <t>维也纳酒店（5.0信阳西亚城店）</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>7天优品Premium(信阳固始县联通大厦店)</t>
+          <t>维也纳酒店(信阳西亚城店)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>30</v>
       </c>
       <c r="Q35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R35" t="n">
         <v>30</v>
@@ -3674,27 +3674,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>周口市</t>
+          <t>信阳市</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>7311990964497680396</t>
+          <t>7192882040184768570</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7天酒店（周口五一广场市中心医院店）</t>
+          <t>7天优品Premium（信阳固始县联通大厦店）</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>7天酒店(周口五一广场市中心医院店)</t>
+          <t>7天优品Premium(信阳固始县联通大厦店)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H36" t="n">
